--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0003T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0003T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.84287348604527</v>
+        <v>4.036966941482356</v>
       </c>
       <c r="D2" t="n">
-        <v>24.3176785961297</v>
+        <v>3.951622771871076</v>
       </c>
       <c r="E2" t="n">
-        <v>20.37555235650285</v>
+        <v>3.311027257931714</v>
       </c>
       <c r="F2" t="n">
-        <v>16.55461912066113</v>
+        <v>2.690125607107434</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.88331238669639</v>
+        <v>3.231038262838163</v>
       </c>
       <c r="D3" t="n">
-        <v>20.76130785284319</v>
+        <v>3.373712526087019</v>
       </c>
       <c r="E3" t="n">
-        <v>20.37555235650285</v>
+        <v>3.311027257931714</v>
       </c>
       <c r="F3" t="n">
-        <v>16.55461912066113</v>
+        <v>2.690125607107434</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>48.71751121519392</v>
+        <v>7.916595572469012</v>
       </c>
       <c r="D4" t="n">
-        <v>16.64476646495281</v>
+        <v>2.704774550554832</v>
       </c>
       <c r="E4" t="n">
-        <v>20.37555235650285</v>
+        <v>3.311027257931714</v>
       </c>
       <c r="F4" t="n">
-        <v>16.55461912066113</v>
+        <v>2.690125607107434</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>64.20382342852191</v>
+        <v>10.43312130713481</v>
       </c>
       <c r="D5" t="n">
-        <v>61.83484643286787</v>
+        <v>10.04816254534103</v>
       </c>
       <c r="E5" t="n">
-        <v>20.37555235650285</v>
+        <v>3.311027257931714</v>
       </c>
       <c r="F5" t="n">
-        <v>16.55461912066113</v>
+        <v>2.690125607107434</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>70.65607027015693</v>
+        <v>11.4816114189005</v>
       </c>
       <c r="D6" t="n">
-        <v>21.94670155524521</v>
+        <v>3.566339002727346</v>
       </c>
       <c r="E6" t="n">
-        <v>20.37555235650285</v>
+        <v>3.311027257931714</v>
       </c>
       <c r="F6" t="n">
-        <v>16.55461912066113</v>
+        <v>2.690125607107434</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
